--- a/Donnees/Statistiques Economiques/Climatologie (3).xlsx
+++ b/Donnees/Statistiques Economiques/Climatologie (3).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Ansade_Project\Donnees\Statistiques Economiques\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{370B1EC9-1458-4E5F-88D7-F54627258B63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0525B677-0FD4-4095-8CFF-D880894BECE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tempe1" sheetId="7" r:id="rId1"/>
